--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monthcard.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monthcard.xlsx
@@ -1399,7 +1399,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="1">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="G5" s="1">
         <v>3001</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monthcard.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_monthcard.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="monthcard" sheetId="1" r:id="rId1"/>
@@ -87,7 +92,7 @@
     <t>30031062#30032003</t>
   </si>
   <si>
-    <t>解锁功能：世界聊天#解锁功能：随身商店#解锁功能：随身仓库#解锁功能：自动回收、拾取#解锁功能：自动维修、买药#解锁功能：交易行上架#解锁功能：面对面交易#解锁功能：材料解绑#解锁功能：宝石解绑#解锁功能：宝石爆率*200%</t>
+    <t>解锁功能：世界聊天#解锁功能：随身商店#解锁功能：随身仓库#解锁功能：自动回收、拾取#解锁功能：自动维修、买药#解锁功能：交易行上架#解锁功能：材料解绑#解锁功能：宝石解绑#解锁功能：宝石爆率*200%</t>
   </si>
   <si>
     <t>至尊卡1天</t>
@@ -96,7 +101,7 @@
     <t>30031063#30032001</t>
   </si>
   <si>
-    <t>解锁功能：交易行上架#解锁功能：面对面交易#解锁功能：材料解绑#解锁功能：宝石解绑#解锁功能：宝石爆率*200%</t>
+    <t>解锁功能：交易行上架#解锁功能：材料解绑#解锁功能：宝石解绑#解锁功能：宝石爆率*200%</t>
   </si>
   <si>
     <t>至尊卡30天</t>
